--- a/reports/telegram/aegis_daily_2026-08-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -445,41 +445,40 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="44" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="6" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="9" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="8" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="15" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="11" customWidth="1" min="43" max="43"/>
-    <col width="32" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
-    <col width="18" customWidth="1" min="46" max="46"/>
-    <col width="17" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="8" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="32" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="18" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -550,182 +549,177 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Risk Meter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Risk Meter</t>
+          <t>Adj Conf</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Adj Conf</t>
+          <t>Ctx Drag</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Drag</t>
+          <t>Ctx Reason</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Reason</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Confidence %</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Confidence %</t>
+          <t>Conf Type</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Conf Type</t>
+          <t>Model Score</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Model Score</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Trading Days</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Trading Days</t>
+          <t>Horizon (d)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Horizon (d)</t>
+          <t>Days Left</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Days Left</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Current Price</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Current Price</t>
+          <t>Entry Price</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Entry Price</t>
+          <t>Buy Zone Low</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone Low</t>
+          <t>Buy Zone High</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone High</t>
+          <t>Stop Loss</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Stop Loss</t>
+          <t>Risk %</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Risk %</t>
+          <t>Target 1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Target 1</t>
+          <t>T1 %</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>T1 %</t>
+          <t>Target 2</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Target 2</t>
+          <t>T2 %</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>T2 %</t>
+          <t>Prev Close</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Prev Close</t>
+          <t>Today Move %</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Today Move %</t>
+          <t>Current Perf %</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Current Perf %</t>
+          <t>Max Gain %</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Max Gain %</t>
+          <t>Max DD %</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Max DD %</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio Weight %</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV1"/>
+  <autoFilter ref="A1:AU1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>